--- a/cds/mm_belgium-5year-cds.xlsx
+++ b/cds/mm_belgium-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="680">
   <si>
     <t>Date</t>
   </si>
@@ -2040,6 +2040,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2389,7 +2404,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B674"/>
+  <dimension ref="A1:B679"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7782,6 +7797,46 @@
       </c>
       <c r="B674" s="3">
         <v>17.1338</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B675" s="3">
+        <v>18.2577</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B676" s="3">
+        <v>18.6637</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B677" s="3">
+        <v>22.0568</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B678" s="3">
+        <v>21.524</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B679" s="3">
+        <v>20.9545</v>
       </c>
     </row>
   </sheetData>
